--- a/data/trans_bre/IP11-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP11-Estudios-trans_bre.xlsx
@@ -660,37 +660,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 6,14</t>
+          <t>-3,5; 5,83</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-18,44; -2,83</t>
+          <t>-18,92; -3,22</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 6,07</t>
+          <t>-3,85; 6,33</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,51; 3,56</t>
+          <t>-7,32; 3,63</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-72,57; 620,65</t>
+          <t>-71,08; 483,26</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-89,18; -23,27</t>
+          <t>-90,01; -22,55</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-81,86; 660,33</t>
+          <t>-79,09; 653,69</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,19; 0,01</t>
+          <t>-5,4; -0,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 2,19</t>
+          <t>-3,58; 2,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,3; -0,65</t>
+          <t>-5,24; -0,94</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 1,49</t>
+          <t>-2,24; 1,55</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-57,09; 1,31</t>
+          <t>-57,99; 1,32</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-34,06; 28,32</t>
+          <t>-34,51; 29,34</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-66,99; -9,2</t>
+          <t>-67,45; -17,49</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-57,65; 81,53</t>
+          <t>-59,84; 84,76</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 5,84</t>
+          <t>-2,05; 5,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,16; 1,57</t>
+          <t>-8,38; 1,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,94; 1,68</t>
+          <t>-4,01; 1,9</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 2,81</t>
+          <t>-4,76; 3,08</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-44,23; 217,31</t>
+          <t>-38,19; 259,93</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-68,51; 27,54</t>
+          <t>-67,71; 19,05</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-76,84; 93,67</t>
+          <t>-77,89; 102,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-75,01; 157,07</t>
+          <t>-76,82; 204,12</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 0,77</t>
+          <t>-3,27; 0,7</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,28; -0,28</t>
+          <t>-4,82; -0,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,94; -0,26</t>
+          <t>-3,93; -0,35</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 1,13</t>
+          <t>-2,33; 0,88</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-44,48; 14,51</t>
+          <t>-42,7; 15,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-46,64; -2,32</t>
+          <t>-44,24; -1,11</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-60,09; -5,16</t>
+          <t>-59,28; -6,11</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-51,95; 48,03</t>
+          <t>-56,77; 38,42</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP11-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP11-Estudios-trans_bre.xlsx
@@ -660,37 +660,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 5,83</t>
+          <t>-3,49; 5,94</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-18,92; -3,22</t>
+          <t>-17,77; -3,03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 6,33</t>
+          <t>-4,58; 6,28</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,32; 3,63</t>
+          <t>-8,33; 3,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-71,08; 483,26</t>
+          <t>-69,24; 490,65</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-90,01; -22,55</t>
+          <t>-89,0; -22,85</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-79,09; 653,69</t>
+          <t>-81,14; 451,71</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0,47</t>
+          <t>-0,46</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-16,27%</t>
+          <t>-16,13%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,4; -0,11</t>
+          <t>-5,23; -0,13</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 2,18</t>
+          <t>-3,65; 2,52</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,24; -0,94</t>
+          <t>-5,14; -0,72</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 1,55</t>
+          <t>-2,22; 1,19</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-57,99; 1,32</t>
+          <t>-57,84; -1,88</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-34,51; 29,34</t>
+          <t>-34,12; 35,43</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-67,45; -17,49</t>
+          <t>-66,96; -11,68</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-59,84; 84,76</t>
+          <t>-60,19; 62,5</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 5,8</t>
+          <t>-1,96; 5,48</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,38; 1,19</t>
+          <t>-7,99; 1,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 1,9</t>
+          <t>-3,98; 1,98</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 3,08</t>
+          <t>-5,12; 2,59</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-38,19; 259,93</t>
+          <t>-37,15; 230,5</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-67,71; 19,05</t>
+          <t>-68,78; 21,15</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-77,89; 102,0</t>
+          <t>-77,83; 138,44</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-76,82; 204,12</t>
+          <t>-75,35; 152,88</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0,58</t>
+          <t>-0,57</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-18,26%</t>
+          <t>-18,16%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 0,7</t>
+          <t>-3,62; 0,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,82; -0,06</t>
+          <t>-4,98; -0,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,93; -0,35</t>
+          <t>-3,85; -0,35</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 0,88</t>
+          <t>-2,32; 0,96</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-42,7; 15,04</t>
+          <t>-46,61; 9,79</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-44,24; -1,11</t>
+          <t>-44,93; -0,48</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-59,28; -6,11</t>
+          <t>-60,74; -7,4</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-56,77; 38,42</t>
+          <t>-55,05; 41,64</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP11-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP11-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0,2</t>
+          <t>0,4</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-9,11%</t>
+          <t>19,67%</t>
         </is>
       </c>
     </row>
@@ -660,37 +660,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 5,94</t>
+          <t>-3,58; 6,14</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-17,77; -3,03</t>
+          <t>-18,44; -2,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,58; 6,28</t>
+          <t>-4,51; 6,07</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,33; 3,35</t>
+          <t>-5,98; 5,17</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-69,24; 490,65</t>
+          <t>-72,57; 620,65</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-89,0; -22,85</t>
+          <t>-89,18; -23,27</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-81,14; 451,71</t>
+          <t>-81,86; 660,33</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0,46</t>
+          <t>-0,34</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-16,13%</t>
+          <t>-11,87%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,23; -0,13</t>
+          <t>-5,19; 0,01</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 2,52</t>
+          <t>-3,61; 2,19</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,14; -0,72</t>
+          <t>-5,3; -0,65</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 1,19</t>
+          <t>-2,24; 1,56</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-57,84; -1,88</t>
+          <t>-57,09; 1,31</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-34,12; 35,43</t>
+          <t>-34,06; 28,32</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-66,96; -11,68</t>
+          <t>-66,99; -9,2</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-60,19; 62,5</t>
+          <t>-59,38; 87,13</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,95</t>
+          <t>-1,0</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-21,99%</t>
+          <t>-22,91%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 5,48</t>
+          <t>-2,28; 5,84</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,99; 1,0</t>
+          <t>-8,16; 1,57</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,98; 1,98</t>
+          <t>-3,94; 1,68</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,12; 2,59</t>
+          <t>-4,95; 2,8</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-37,15; 230,5</t>
+          <t>-44,23; 217,31</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-68,78; 21,15</t>
+          <t>-68,51; 27,54</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-77,83; 138,44</t>
+          <t>-76,84; 93,67</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-75,35; 152,88</t>
+          <t>-75,44; 163,59</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0,57</t>
+          <t>-0,44</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-18,16%</t>
+          <t>-13,93%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 0,57</t>
+          <t>-3,36; 0,77</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,98; -0,05</t>
+          <t>-5,28; -0,28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,85; -0,35</t>
+          <t>-3,94; -0,26</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 0,96</t>
+          <t>-1,97; 1,03</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-46,61; 9,79</t>
+          <t>-44,48; 14,51</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-44,93; -0,48</t>
+          <t>-46,64; -2,32</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-60,74; -7,4</t>
+          <t>-60,09; -5,16</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-55,05; 41,64</t>
+          <t>-52,14; 52,02</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP11-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP11-Estudios-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,195 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>1,26</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-10,21</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,45</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,4</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>38,48%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-69,95%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>12,27%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>19,67%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>1.258147595026553</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-10.21310924026902</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.452147571728366</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>0.3954795343479318</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.3848129773374835</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.6995045184497782</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>0.1226809190569865</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>0.1967112248102358</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-3,58; 6,14</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-18,44; -2,83</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-4,51; 6,07</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-5,98; 5,17</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-72,57; 620,65</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-89,18; -23,27</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-81,86; 660,33</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-3.579285104777989</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-18.43522128128253</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-4.506933788160968</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-5.984491698391134</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.7257437863522621</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.8918033567463116</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.818579883483983</v>
+      </c>
+      <c r="J5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>6.13734130781072</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>-2.826811688614517</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>6.069161893901603</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>5.169785463933858</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>6.206479818817261</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>-0.2327485787875602</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>6.60333488381139</v>
+      </c>
+      <c r="J6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-2,68</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-0,71</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-2,93</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-0,34</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-34,66%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-7,8%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-45,61%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-11,87%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-5,19; 0,01</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-3,61; 2,19</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-5,3; -0,65</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-2,24; 1,56</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-57,09; 1,31</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-34,06; 28,32</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-66,99; -9,2</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-59,38; 87,13</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-2.682499877610504</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-0.7108106979887285</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-2.933295403844324</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-0.3434384079648259</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.3465513570458493</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.07801879520218381</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-0.4560885808847759</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.1187446697778628</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>1,55</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-3,45</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-1,06</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-1,0</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>36,24%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-37,23%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-29,17%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-22,91%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-5.192549213073556</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-3.607118286139176</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-5.296382667314072</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-2.237177499910833</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.5708766710940809</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.3405610000988362</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.6699253002453922</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.5938315965745968</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-2,28; 5,84</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-8,16; 1,57</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-3,94; 1,68</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-4,95; 2,8</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-44,23; 217,31</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-68,51; 27,54</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-76,84; 93,67</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-75,44; 163,59</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.0124347012271243</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>2.190318850522027</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>-0.6487992396038049</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>1.555254965355624</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.01307661628850156</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.2832473903737382</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>-0.09196193265624908</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.8713298536604667</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,97 +815,197 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-1,26</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-2,5</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-2,15</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-0,44</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-19,56%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-25,62%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-39,23%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-13,93%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>1.549990492130741</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-3.45149030831968</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-1.062634022422152</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-1.003900985728039</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.3623616584096774</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.372268969601233</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.2917048673750814</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.2290508524577023</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-3,36; 0,77</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-5,28; -0,28</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-3,94; -0,26</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-1,97; 1,03</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-44,48; 14,51</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-46,64; -2,32</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-60,09; -5,16</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-52,14; 52,02</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-2.280415844490536</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-8.156300440123635</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-3.937469980461288</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-4.948559154481088</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.4422702716818055</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.6850685840807738</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.7684302054607581</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.754360004377609</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>5.836704647187001</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>1.567393750021231</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>1.680412330384</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>2.79899399903105</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>2.173073068451707</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.275443419533744</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.9366770541311603</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>1.635864270766922</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-1.260260511315733</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-2.504693308313488</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-2.148717405378005</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-0.4430584729603438</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.1955650311358964</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.2561552693706425</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.392291843862993</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.1393489230100027</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-3.355321794267677</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-5.276835056606783</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-3.941335189188385</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-1.965856408320511</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.4447995741565474</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.4664415696821517</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.6008887846541371</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.5214186363633971</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.7714413785057728</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>-0.2787903185048259</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>-0.2615262235720526</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>1.031901601705945</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.1450855714923901</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>-0.0232401936222113</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>-0.05163889896638876</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.5201679624178976</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1008,13 +1013,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
